--- a/results/components/gene_names/p4s6.xlsx
+++ b/results/components/gene_names/p4s6.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>gene1</t>
   </si>
@@ -22,58 +22,79 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Psn</t>
-  </si>
-  <si>
-    <t>Ark</t>
-  </si>
-  <si>
-    <t>Akt1</t>
-  </si>
-  <si>
-    <t>Rack1</t>
-  </si>
-  <si>
-    <t>Dcp-1</t>
-  </si>
-  <si>
-    <t>ix</t>
-  </si>
-  <si>
-    <t>Dhc64C</t>
-  </si>
-  <si>
-    <t>CG34417</t>
-  </si>
-  <si>
-    <t>Rbp9</t>
-  </si>
-  <si>
-    <t>noc</t>
-  </si>
-  <si>
-    <t>cnc</t>
-  </si>
-  <si>
-    <t>Tak1</t>
-  </si>
-  <si>
-    <t>Mitf</t>
-  </si>
-  <si>
-    <t>mask</t>
-  </si>
-  <si>
-    <t>cin</t>
-  </si>
-  <si>
-    <t>thr</t>
-  </si>
-  <si>
-    <t>ttk</t>
-  </si>
-  <si>
-    <t>ALiX</t>
+    <t>Ef1gamma</t>
+  </si>
+  <si>
+    <t>tin</t>
+  </si>
+  <si>
+    <t>Dif</t>
+  </si>
+  <si>
+    <t>Rca1</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>Sema-2a</t>
+  </si>
+  <si>
+    <t>cbt</t>
+  </si>
+  <si>
+    <t>CG12301</t>
+  </si>
+  <si>
+    <t>Idgf4</t>
+  </si>
+  <si>
+    <t>ine</t>
+  </si>
+  <si>
+    <t>Cka</t>
+  </si>
+  <si>
+    <t>Pk92B</t>
+  </si>
+  <si>
+    <t>sgg</t>
+  </si>
+  <si>
+    <t>pot</t>
+  </si>
+  <si>
+    <t>Bap60</t>
+  </si>
+  <si>
+    <t>Dat</t>
+  </si>
+  <si>
+    <t>bon</t>
+  </si>
+  <si>
+    <t>esc</t>
+  </si>
+  <si>
+    <t>sas</t>
+  </si>
+  <si>
+    <t>spen</t>
+  </si>
+  <si>
+    <t>lmd</t>
+  </si>
+  <si>
+    <t>gl</t>
+  </si>
+  <si>
+    <t>hpo</t>
+  </si>
+  <si>
+    <t>Eip63E</t>
+  </si>
+  <si>
+    <t>abd-A</t>
   </si>
 </sst>
 </file>
@@ -405,7 +426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -488,6 +509,38 @@
         <v>19</v>
       </c>
     </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/components/gene_names/p4s6.xlsx
+++ b/results/components/gene_names/p4s6.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>gene1</t>
   </si>
@@ -22,79 +22,10 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Ef1gamma</t>
+    <t>kuk</t>
   </si>
   <si>
-    <t>tin</t>
-  </si>
-  <si>
-    <t>Dif</t>
-  </si>
-  <si>
-    <t>Rca1</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>Sema-2a</t>
-  </si>
-  <si>
-    <t>cbt</t>
-  </si>
-  <si>
-    <t>CG12301</t>
-  </si>
-  <si>
-    <t>Idgf4</t>
-  </si>
-  <si>
-    <t>ine</t>
-  </si>
-  <si>
-    <t>Cka</t>
-  </si>
-  <si>
-    <t>Pk92B</t>
-  </si>
-  <si>
-    <t>sgg</t>
-  </si>
-  <si>
-    <t>pot</t>
-  </si>
-  <si>
-    <t>Bap60</t>
-  </si>
-  <si>
-    <t>Dat</t>
-  </si>
-  <si>
-    <t>bon</t>
-  </si>
-  <si>
-    <t>esc</t>
-  </si>
-  <si>
-    <t>sas</t>
-  </si>
-  <si>
-    <t>spen</t>
-  </si>
-  <si>
-    <t>lmd</t>
-  </si>
-  <si>
-    <t>gl</t>
-  </si>
-  <si>
-    <t>hpo</t>
-  </si>
-  <si>
-    <t>Eip63E</t>
-  </si>
-  <si>
-    <t>abd-A</t>
+    <t>neur</t>
   </si>
 </sst>
 </file>
@@ -426,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -445,102 +376,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
